--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-change-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
